--- a/historico_ordens.xlsx
+++ b/historico_ordens.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1795,7 +1795,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="1" t="n">
         <v>46275</v>
       </c>
       <c r="B66" t="inlineStr">
@@ -1813,6 +1813,48 @@
       </c>
       <c r="E66" t="n">
         <v>8</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>CMIN3</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>6.230000019073486</v>
+      </c>
+      <c r="E67" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>USIM5</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>7.03000020980835</v>
+      </c>
+      <c r="E68" t="n">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/historico_ordens.xlsx
+++ b/historico_ordens.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E68"/>
+  <dimension ref="A1:E71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1816,7 +1816,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="1" t="n">
         <v>46279</v>
       </c>
       <c r="B67" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="1" t="n">
         <v>46279</v>
       </c>
       <c r="B68" t="inlineStr">
@@ -1855,6 +1855,69 @@
       </c>
       <c r="E68" t="n">
         <v>11</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>ALPA4</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>12.86999988555908</v>
+      </c>
+      <c r="E69" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>BEEF3</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>3.819999933242798</v>
+      </c>
+      <c r="E70" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>POMO4</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>4.320000171661377</v>
+      </c>
+      <c r="E71" t="n">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/historico_ordens.xlsx
+++ b/historico_ordens.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E71"/>
+  <dimension ref="A1:E72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1858,7 +1858,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="1" t="n">
         <v>46282</v>
       </c>
       <c r="B69" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="1" t="n">
         <v>46282</v>
       </c>
       <c r="B70" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="1" t="n">
         <v>46282</v>
       </c>
       <c r="B71" t="inlineStr">
@@ -1918,6 +1918,27 @@
       </c>
       <c r="E71" t="n">
         <v>20</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>PRIO3</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>60.79999923706055</v>
+      </c>
+      <c r="E72" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/historico_ordens.xlsx
+++ b/historico_ordens.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E72"/>
+  <dimension ref="A1:E73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1921,7 +1921,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="1" t="n">
         <v>46286</v>
       </c>
       <c r="B72" t="inlineStr">
@@ -1939,6 +1939,27 @@
       </c>
       <c r="E72" t="n">
         <v>8</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>ALPA4</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Compra</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>13.77999973297119</v>
+      </c>
+      <c r="E73" t="n">
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/historico_ordens.xlsx
+++ b/historico_ordens.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E73"/>
+  <dimension ref="A1:E75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1942,7 +1942,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="1" t="n">
         <v>46287</v>
       </c>
       <c r="B73" t="inlineStr">
@@ -1960,6 +1960,48 @@
       </c>
       <c r="E73" t="n">
         <v>31</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>BEEF3</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Compra</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>4.070000171661377</v>
+      </c>
+      <c r="E74" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>SUZB3</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>45.52999877929688</v>
+      </c>
+      <c r="E75" t="n">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/historico_ordens.xlsx
+++ b/historico_ordens.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E75"/>
+  <dimension ref="A1:E76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1963,7 +1963,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="1" t="n">
         <v>46289</v>
       </c>
       <c r="B74" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="1" t="n">
         <v>46289</v>
       </c>
       <c r="B75" t="inlineStr">
@@ -2002,6 +2002,27 @@
       </c>
       <c r="E75" t="n">
         <v>11</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>RADL3</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>18.13999938964844</v>
+      </c>
+      <c r="E76" t="n">
+        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/historico_ordens.xlsx
+++ b/historico_ordens.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E76"/>
+  <dimension ref="A1:E77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2005,7 +2005,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="1" t="n">
         <v>46290</v>
       </c>
       <c r="B76" t="inlineStr">
@@ -2023,6 +2023,27 @@
       </c>
       <c r="E76" t="n">
         <v>63</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>ENEV3</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>26.79000091552734</v>
+      </c>
+      <c r="E77" t="n">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/historico_ordens.xlsx
+++ b/historico_ordens.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E77"/>
+  <dimension ref="A1:E78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2026,7 +2026,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="1" t="n">
         <v>46293</v>
       </c>
       <c r="B77" t="inlineStr">
@@ -2044,6 +2044,27 @@
       </c>
       <c r="E77" t="n">
         <v>20</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>CSNA3</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>5.380000114440918</v>
+      </c>
+      <c r="E78" t="n">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/historico_ordens.xlsx
+++ b/historico_ordens.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E78"/>
+  <dimension ref="A1:E79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2047,7 +2047,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="1" t="n">
         <v>46294</v>
       </c>
       <c r="B78" t="inlineStr">
@@ -2065,6 +2065,27 @@
       </c>
       <c r="E78" t="n">
         <v>22</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>ENEV3</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Compra</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>27.95000076293945</v>
+      </c>
+      <c r="E79" t="n">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/historico_ordens.xlsx
+++ b/historico_ordens.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E79"/>
+  <dimension ref="A1:E80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2068,7 +2068,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" s="1" t="n">
         <v>46295</v>
       </c>
       <c r="B79" t="inlineStr">
@@ -2086,6 +2086,27 @@
       </c>
       <c r="E79" t="n">
         <v>20</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>USIM5</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Compra</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>7.130000114440918</v>
+      </c>
+      <c r="E80" t="n">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/historico_ordens.xlsx
+++ b/historico_ordens.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E80"/>
+  <dimension ref="A1:E84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2089,7 +2089,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="1" t="n">
         <v>46296</v>
       </c>
       <c r="B80" t="inlineStr">
@@ -2107,6 +2107,90 @@
       </c>
       <c r="E80" t="n">
         <v>11</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>BEEF3</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>3.880000114440918</v>
+      </c>
+      <c r="E81" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>MRVE3</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Compra</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>5.610000133514404</v>
+      </c>
+      <c r="E82" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>PRIO3</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Compra</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>63.04000091552734</v>
+      </c>
+      <c r="E83" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>PSSA3</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Compra</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="E84" t="n">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/historico_ordens.xlsx
+++ b/historico_ordens.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E84"/>
+  <dimension ref="A1:E86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2110,7 +2110,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n">
+      <c r="A81" s="1" t="n">
         <v>46297</v>
       </c>
       <c r="B81" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="A82" s="1" t="n">
         <v>46297</v>
       </c>
       <c r="B82" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n">
+      <c r="A83" s="1" t="n">
         <v>46297</v>
       </c>
       <c r="B83" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
+      <c r="A84" s="1" t="n">
         <v>46297</v>
       </c>
       <c r="B84" t="inlineStr">
@@ -2191,6 +2191,48 @@
       </c>
       <c r="E84" t="n">
         <v>16</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>BEEF3</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Compra</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>4.190000057220459</v>
+      </c>
+      <c r="E85" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>POMO4</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Compra</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>4.699999809265137</v>
+      </c>
+      <c r="E86" t="n">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/historico_ordens.xlsx
+++ b/historico_ordens.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E86"/>
+  <dimension ref="A1:E87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2194,7 +2194,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
+      <c r="A85" s="1" t="n">
         <v>46300</v>
       </c>
       <c r="B85" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="1" t="n">
         <v>46300</v>
       </c>
       <c r="B86" t="inlineStr">
@@ -2233,6 +2233,27 @@
       </c>
       <c r="E86" t="n">
         <v>20</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>CMIN3</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Compra</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>5.110000133514404</v>
+      </c>
+      <c r="E87" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/historico_ordens.xlsx
+++ b/historico_ordens.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E87"/>
+  <dimension ref="A1:E88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2236,7 +2236,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" s="1" t="n">
         <v>46303</v>
       </c>
       <c r="B87" t="inlineStr">
@@ -2254,6 +2254,27 @@
       </c>
       <c r="E87" t="n">
         <v>10</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>CSNA3</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Compra</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>6.570000171661377</v>
+      </c>
+      <c r="E88" t="n">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/historico_ordens.xlsx
+++ b/historico_ordens.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E88"/>
+  <dimension ref="A1:E89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2257,7 +2257,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="1" t="n">
         <v>46304</v>
       </c>
       <c r="B88" t="inlineStr">
@@ -2274,6 +2274,27 @@
         <v>6.570000171661377</v>
       </c>
       <c r="E88" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>CSNA3</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Compra</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>6.610000133514404</v>
+      </c>
+      <c r="E89" t="n">
         <v>22</v>
       </c>
     </row>

--- a/historico_ordens.xlsx
+++ b/historico_ordens.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E89"/>
+  <dimension ref="A1:E90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2278,7 +2278,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="A89" s="1" t="n">
         <v>46307</v>
       </c>
       <c r="B89" t="inlineStr">
@@ -2296,6 +2296,27 @@
       </c>
       <c r="E89" t="n">
         <v>22</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>BHIA3</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Compra</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>1.450000047683716</v>
+      </c>
+      <c r="E90" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/historico_ordens.xlsx
+++ b/historico_ordens.xlsx
@@ -16,11 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E90"/>
+  <dimension ref="A1:E106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1250,95 +1247,95 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>46255</v>
+        <v>46254</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>EZTC3</t>
+          <t>BHIA3</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Compra</t>
+          <t>Venda</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.27</v>
+        <v>0.41</v>
       </c>
       <c r="E40" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>46255</v>
+        <v>46254</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>RADL3</t>
+          <t>BRKM5</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Compra</t>
+          <t>Venda</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>18.43</v>
+        <v>5.1</v>
       </c>
       <c r="E41" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>46258</v>
+        <v>46254</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CSNA3</t>
+          <t>EZTC3</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Compra</t>
+          <t>Venda</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>5.16</v>
+        <v>10.51</v>
       </c>
       <c r="E42" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>46258</v>
+        <v>46254</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ENEV3</t>
+          <t>MOVI3</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Compra</t>
+          <t>Venda</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>26.1</v>
+        <v>6.5</v>
       </c>
       <c r="E43" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>46258</v>
+        <v>46254</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>USIM5</t>
+          <t>PETR4</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1347,40 +1344,40 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>7.12</v>
+        <v>44.32</v>
       </c>
       <c r="E44" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>46259</v>
+        <v>46254</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>HYPE3</t>
+          <t>POMO4</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Compra</t>
+          <t>Venda</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>21.8</v>
+        <v>4.45</v>
       </c>
       <c r="E45" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>46259</v>
+        <v>46254</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>RDOR3</t>
+          <t>PRIO3</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1389,61 +1386,61 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>36.07</v>
+        <v>62.04</v>
       </c>
       <c r="E46" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>46261</v>
+        <v>46254</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>MGLU3</t>
+          <t>RDOR3</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Compra</t>
+          <t>Venda</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>4.710000038146973</v>
+        <v>33.75</v>
       </c>
       <c r="E47" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46265</v>
+        <v>46254</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ALOS3</t>
+          <t>SMAL11</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Compra</t>
+          <t>Venda</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>26.69</v>
+        <v>99.25</v>
       </c>
       <c r="E48" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46265</v>
+        <v>46254</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BHIA3</t>
+          <t>VBBR3</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1452,19 +1449,19 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0.66</v>
+        <v>34.47</v>
       </c>
       <c r="E49" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46265</v>
+        <v>46255</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>JHSF3</t>
+          <t>EZTC3</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1473,19 +1470,19 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>10.9</v>
+        <v>11.27</v>
       </c>
       <c r="E50" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46265</v>
+        <v>46255</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>PRIO3</t>
+          <t>RADL3</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1494,19 +1491,19 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>62.68</v>
+        <v>18.43</v>
       </c>
       <c r="E51" t="n">
-        <v>8</v>
+        <v>63</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46265</v>
+        <v>46258</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PSSA3</t>
+          <t>CSNA3</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1515,19 +1512,19 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>49.08</v>
+        <v>5.16</v>
       </c>
       <c r="E52" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46265</v>
+        <v>46258</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SMAL11</t>
+          <t>ENEV3</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1536,19 +1533,19 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>106.13</v>
+        <v>26.1</v>
       </c>
       <c r="E53" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46266</v>
+        <v>46258</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ALOS3</t>
+          <t>USIM5</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1557,19 +1554,19 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>26.69000053405762</v>
+        <v>7.12</v>
       </c>
       <c r="E54" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46266</v>
+        <v>46259</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BHIA3</t>
+          <t>HYPE3</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1578,19 +1575,19 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.6600000262260437</v>
+        <v>21.8</v>
       </c>
       <c r="E55" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46266</v>
+        <v>46259</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JHSF3</t>
+          <t>RDOR3</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1599,19 +1596,19 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>10.89999961853027</v>
+        <v>36.07</v>
       </c>
       <c r="E56" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46266</v>
+        <v>46261</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PRIO3</t>
+          <t>BOVA11</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1620,19 +1617,19 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>62.68000030517578</v>
+        <v>171.82</v>
       </c>
       <c r="E57" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46266</v>
+        <v>46261</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PSSA3</t>
+          <t>MGLU3</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1641,19 +1638,19 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>49.08000183105469</v>
+        <v>4.71</v>
       </c>
       <c r="E58" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SMAL11</t>
+          <t>ALOS3</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1662,15 +1659,15 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>106.129997253418</v>
+        <v>26.69</v>
       </c>
       <c r="E59" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -1683,7 +1680,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>20.17000007629395</v>
+        <v>20.74</v>
       </c>
       <c r="E60" t="n">
         <v>30</v>
@@ -1691,32 +1688,32 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>PRIO3</t>
+          <t>BHIA3</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Venda</t>
+          <t>Compra</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>60.54000091552734</v>
+        <v>0.66</v>
       </c>
       <c r="E61" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46267</v>
+        <v>46265</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>MOVI3</t>
+          <t>JHSF3</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1725,61 +1722,61 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>7.849999904632568</v>
+        <v>10.9</v>
       </c>
       <c r="E62" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46269</v>
+        <v>46265</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PRIO3</t>
+          <t>PSSA3</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Venda</t>
+          <t>Compra</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>60.22999954223633</v>
+        <v>49.08</v>
       </c>
       <c r="E63" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46272</v>
+        <v>46265</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PRIO3</t>
+          <t>SMAL11</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Venda</t>
+          <t>Compra</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>60.18999862670898</v>
+        <v>106.13</v>
       </c>
       <c r="E64" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46273</v>
+        <v>46267</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CXSE3</t>
+          <t>BPAC11</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1788,19 +1785,19 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>20.20999908447266</v>
+        <v>57.70000076293945</v>
       </c>
       <c r="E65" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46275</v>
+        <v>46267</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PRIO3</t>
+          <t>MOVI3</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1809,40 +1806,40 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>64.23999786376953</v>
+        <v>7.849999904632568</v>
       </c>
       <c r="E66" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46279</v>
+        <v>46267</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CMIN3</t>
+          <t>POMO4</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Venda</t>
+          <t>Compra</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>6.230000019073486</v>
+        <v>4.619999885559082</v>
       </c>
       <c r="E67" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46279</v>
+        <v>46269</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>USIM5</t>
+          <t>PRIO3</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -1851,61 +1848,61 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>7.03000020980835</v>
+        <v>60.22999954223633</v>
       </c>
       <c r="E68" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46282</v>
+        <v>46273</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ALPA4</t>
+          <t>CXSE3</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Venda</t>
+          <t>Compra</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>12.86999988555908</v>
+        <v>20.20999908447266</v>
       </c>
       <c r="E69" t="n">
-        <v>31</v>
+        <v>49</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46282</v>
+        <v>46275</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>BEEF3</t>
+          <t>PRIO3</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Venda</t>
+          <t>Compra</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>3.819999933242798</v>
+        <v>64.23999786376953</v>
       </c>
       <c r="E70" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46282</v>
+        <v>46279</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>POMO4</t>
+          <t>CMIN3</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -1914,19 +1911,19 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>4.320000171661377</v>
+        <v>6.230000019073486</v>
       </c>
       <c r="E71" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46286</v>
+        <v>46279</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>PRIO3</t>
+          <t>USIM5</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -1935,15 +1932,15 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>60.79999923706055</v>
+        <v>7.03000020980835</v>
       </c>
       <c r="E72" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46287</v>
+        <v>46282</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -1952,11 +1949,11 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Compra</t>
+          <t>Venda</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>13.77999973297119</v>
+        <v>12.86999988555908</v>
       </c>
       <c r="E73" t="n">
         <v>31</v>
@@ -1964,7 +1961,7 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46289</v>
+        <v>46282</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -1973,11 +1970,11 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Compra</t>
+          <t>Venda</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>4.070000171661377</v>
+        <v>3.819999933242798</v>
       </c>
       <c r="E74" t="n">
         <v>16</v>
@@ -1985,11 +1982,11 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46289</v>
+        <v>46282</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SUZB3</t>
+          <t>POMO4</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -1998,124 +1995,124 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>45.52999877929688</v>
+        <v>4.320000171661377</v>
       </c>
       <c r="E75" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46290</v>
+        <v>46283</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>RADL3</t>
+          <t>ALPA4</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Venda</t>
+          <t>Compra</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>18.13999938964844</v>
+        <v>12.98999977111816</v>
       </c>
       <c r="E76" t="n">
-        <v>63</v>
+        <v>31</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46293</v>
+        <v>46283</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ENEV3</t>
+          <t>BEEF3</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Venda</t>
+          <t>Compra</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>26.79000091552734</v>
+        <v>3.970000028610229</v>
       </c>
       <c r="E77" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46294</v>
+        <v>46283</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CSNA3</t>
+          <t>POMO4</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Venda</t>
+          <t>Compra</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>5.380000114440918</v>
+        <v>4.289999961853027</v>
       </c>
       <c r="E78" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46295</v>
+        <v>46286</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>ENEV3</t>
+          <t>ALPA4</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Compra</t>
+          <t>Venda</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>27.95000076293945</v>
+        <v>13.13000011444092</v>
       </c>
       <c r="E79" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46296</v>
+        <v>46286</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>USIM5</t>
+          <t>BEEF3</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Compra</t>
+          <t>Venda</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>7.130000114440918</v>
+        <v>3.900000095367432</v>
       </c>
       <c r="E80" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46297</v>
+        <v>46286</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>BEEF3</t>
+          <t>POMO4</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2124,61 +2121,61 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>3.880000114440918</v>
+        <v>4.25</v>
       </c>
       <c r="E81" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46297</v>
+        <v>46286</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>MRVE3</t>
+          <t>PRIO3</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Compra</t>
+          <t>Venda</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>5.610000133514404</v>
+        <v>60.79999923706055</v>
       </c>
       <c r="E82" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46297</v>
+        <v>46286</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>PRIO3</t>
+          <t>PSSA3</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Compra</t>
+          <t>Venda</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>63.04000091552734</v>
+        <v>49.41999816894531</v>
       </c>
       <c r="E83" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46297</v>
+        <v>46287</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>PSSA3</t>
+          <t>ALPA4</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2187,15 +2184,15 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>49.5</v>
+        <v>13.77999973297119</v>
       </c>
       <c r="E84" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46300</v>
+        <v>46289</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -2208,7 +2205,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>4.190000057220459</v>
+        <v>4.070000171661377</v>
       </c>
       <c r="E85" t="n">
         <v>16</v>
@@ -2216,106 +2213,442 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46300</v>
+        <v>46289</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>POMO4</t>
+          <t>SUZB3</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Compra</t>
+          <t>Venda</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>4.699999809265137</v>
+        <v>45.52999877929688</v>
       </c>
       <c r="E86" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46303</v>
+        <v>46290</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>CMIN3</t>
+          <t>RADL3</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Compra</t>
+          <t>Venda</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>5.110000133514404</v>
+        <v>18.13999938964844</v>
       </c>
       <c r="E87" t="n">
-        <v>10</v>
+        <v>63</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46304</v>
+        <v>46293</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>CSNA3</t>
+          <t>ENEV3</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Compra</t>
+          <t>Venda</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>6.570000171661377</v>
+        <v>26.79000091552734</v>
       </c>
       <c r="E88" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46307</v>
+        <v>46293</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
+          <t>MRVE3</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>5.230000019073486</v>
+      </c>
+      <c r="E89" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
           <t>CSNA3</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Compra</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>6.610000133514404</v>
-      </c>
-      <c r="E89" t="n">
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>5.380000114440918</v>
+      </c>
+      <c r="E90" t="n">
         <v>22</v>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="n">
+    <row r="91">
+      <c r="A91" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>ENEV3</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Compra</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>27.95000076293945</v>
+      </c>
+      <c r="E91" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>USIM5</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Compra</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>7.130000114440918</v>
+      </c>
+      <c r="E92" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>BEEF3</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>3.880000114440918</v>
+      </c>
+      <c r="E93" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>MRVE3</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Compra</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>5.610000133514404</v>
+      </c>
+      <c r="E94" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>PRIO3</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Compra</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>63.04000091552734</v>
+      </c>
+      <c r="E95" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>PSSA3</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Compra</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="E96" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>BEEF3</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Compra</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>4.190000057220459</v>
+      </c>
+      <c r="E97" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>POMO4</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Compra</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>4.699999809265137</v>
+      </c>
+      <c r="E98" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>RADL3</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Compra</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>21.04999923706055</v>
+      </c>
+      <c r="E99" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>CMIN3</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Compra</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>5.110000133514404</v>
+      </c>
+      <c r="E100" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>CMIN3</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>5.039999961853027</v>
+      </c>
+      <c r="E101" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>CSNA3</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Compra</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>6.570000171661377</v>
+      </c>
+      <c r="E102" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>BHIA3</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>1.120000004768372</v>
+      </c>
+      <c r="E103" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>USIM5</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>6.710000038146973</v>
+      </c>
+      <c r="E104" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>CSNA3</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>5.820000171661377</v>
+      </c>
+      <c r="E105" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="n">
         <v>46315</v>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B106" t="inlineStr">
         <is>
           <t>BHIA3</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Compra</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Compra</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
         <v>1.450000047683716</v>
       </c>
-      <c r="E90" t="n">
+      <c r="E106" t="n">
         <v>12</v>
       </c>
     </row>

--- a/historico_ordens.xlsx
+++ b/historico_ordens.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E106"/>
+  <dimension ref="A1:E107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2652,6 +2652,27 @@
         <v>12</v>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>BHIA3</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>1.409999966621399</v>
+      </c>
+      <c r="E107" t="n">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historico_ordens.xlsx
+++ b/historico_ordens.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E107"/>
+  <dimension ref="A1:E109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2673,6 +2673,48 @@
         <v>12</v>
       </c>
     </row>
+    <row r="108">
+      <c r="A108" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>BHIA3</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Compra</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>1.440000057220459</v>
+      </c>
+      <c r="E108" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>VBBR3</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>35.90000152587891</v>
+      </c>
+      <c r="E109" t="n">
+        <v>48</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historico_ordens.xlsx
+++ b/historico_ordens.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E109"/>
+  <dimension ref="A1:E130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2715,6 +2715,447 @@
         <v>48</v>
       </c>
     </row>
+    <row r="110">
+      <c r="A110" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>ALOS3</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>26.48999977111816</v>
+      </c>
+      <c r="E110" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>ALPA4</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>13.27000045776367</v>
+      </c>
+      <c r="E111" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>BBAS3</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>17.96999931335449</v>
+      </c>
+      <c r="E112" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>BEEF3</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>3.319999933242798</v>
+      </c>
+      <c r="E113" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>BHIA3</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>0.8999999761581421</v>
+      </c>
+      <c r="E114" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>BOVA11</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>174.1000061035156</v>
+      </c>
+      <c r="E115" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>BPAC11</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>60.4900016784668</v>
+      </c>
+      <c r="E116" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>ENEV3</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>26.80999946594238</v>
+      </c>
+      <c r="E117" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>EZTC3</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="E118" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>GMAT3</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>3.660000085830688</v>
+      </c>
+      <c r="E119" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>HYPE3</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>20.55999946594238</v>
+      </c>
+      <c r="E120" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>JHSF3</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>10.89999961853027</v>
+      </c>
+      <c r="E121" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>MGLU3</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>5.380000114440918</v>
+      </c>
+      <c r="E122" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>MOVI3</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>7.710000038146973</v>
+      </c>
+      <c r="E123" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>MRVE3</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>4.699999809265137</v>
+      </c>
+      <c r="E124" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>POMO4</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>4.090000152587891</v>
+      </c>
+      <c r="E125" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>PSSA3</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>48.2400016784668</v>
+      </c>
+      <c r="E126" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>RADL3</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>15.72000026702881</v>
+      </c>
+      <c r="E127" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>RDOR3</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>35.02999877929688</v>
+      </c>
+      <c r="E128" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>SMAL11</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>99.81999969482422</v>
+      </c>
+      <c r="E129" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>SUZB3</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Compra</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>47.63000106811523</v>
+      </c>
+      <c r="E130" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historico_ordens.xlsx
+++ b/historico_ordens.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E130"/>
+  <dimension ref="A1:E131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3156,6 +3156,27 @@
         <v>11</v>
       </c>
     </row>
+    <row r="131">
+      <c r="A131" s="1" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>PETR4</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>52.91999816894531</v>
+      </c>
+      <c r="E131" t="n">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
